--- a/data/trans_orig/Q21A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q21A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que utilizó un servicios de urgencias en el último año</t>
+          <t>Número medio de veces que la población utilizó un servicios de urgencias en el último año (tasa de respuesta: 96,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,55</t>
+          <t>1,2; 1,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,12</t>
+          <t>1,51; 2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,06</t>
+          <t>1,48; 2,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,45</t>
+          <t>1,36; 2,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,01</t>
+          <t>1,53; 2,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,65</t>
+          <t>1,8; 2,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,06</t>
+          <t>1,51; 2,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,73</t>
+          <t>1,41; 1,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,48</t>
+          <t>1,79; 2,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,15</t>
+          <t>1,49; 2,11</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,51</t>
+          <t>1,25; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,59</t>
+          <t>1,3; 1,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,39</t>
+          <t>1,41; 2,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,93</t>
+          <t>1,47; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,97</t>
+          <t>1,59; 1,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,23</t>
+          <t>1,75; 2,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,33</t>
+          <t>1,6; 2,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,23</t>
+          <t>1,7; 2,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,73</t>
+          <t>1,49; 1,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 1,87</t>
+          <t>1,58; 1,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,09</t>
+          <t>1,57; 2,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,47</t>
+          <t>1,66; 2,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,43</t>
+          <t>1,17; 1,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,72</t>
+          <t>1,78; 2,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,86</t>
+          <t>1,36; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,04</t>
+          <t>1,55; 2,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,12</t>
+          <t>1,51; 2,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,11</t>
+          <t>1,71; 2,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,03</t>
+          <t>1,82; 2,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,25</t>
+          <t>2,19; 13,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,79</t>
+          <t>1,4; 1,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,27</t>
+          <t>1,79; 2,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,32</t>
+          <t>1,67; 2,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 12,41</t>
+          <t>2,01; 12,34</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,97</t>
+          <t>1,3; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,82</t>
+          <t>1,41; 1,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,76</t>
+          <t>1,42; 1,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,16</t>
+          <t>1,49; 2,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,0</t>
+          <t>1,56; 2,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 1,96</t>
+          <t>1,49; 1,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,22</t>
+          <t>1,69; 2,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,34</t>
+          <t>1,62; 2,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,84</t>
+          <t>1,51; 1,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,85</t>
+          <t>1,49; 1,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,94</t>
+          <t>1,63; 1,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,17</t>
+          <t>1,63; 2,1</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,48</t>
+          <t>1,29; 1,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,97</t>
+          <t>1,58; 1,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,83</t>
+          <t>1,5; 1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,6; 2,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,86</t>
+          <t>1,63; 1,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,05</t>
+          <t>1,78; 2,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,12</t>
+          <t>1,76; 2,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,29</t>
+          <t>1,89; 9,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,67</t>
+          <t>1,52; 1,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,9</t>
+          <t>1,68; 1,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,74</t>
+          <t>1,82; 7,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q21A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q21A-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,56</t>
+          <t>1,18; 1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,87</t>
+          <t>1,51; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,04</t>
+          <t>1,48; 2,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,55</t>
+          <t>1,42; 2,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,05</t>
+          <t>1,52; 2,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,68</t>
+          <t>1,82; 2,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,04</t>
+          <t>1,49; 2,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,25</t>
+          <t>1,52; 2,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,75</t>
+          <t>1,39; 1,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,5</t>
+          <t>1,78; 2,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,93</t>
+          <t>1,55; 1,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,11</t>
+          <t>1,52; 2,14</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,5</t>
+          <t>1,25; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,58</t>
+          <t>1,3; 1,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,31</t>
+          <t>1,4; 2,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,92</t>
+          <t>1,5; 3,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,37 +881,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,24</t>
+          <t>1,77; 2,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,29</t>
+          <t>1,61; 2,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,24</t>
+          <t>1,7; 2,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,73</t>
+          <t>1,49; 1,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,9</t>
+          <t>1,59; 1,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,07</t>
+          <t>1,56; 2,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,43</t>
+          <t>1,67; 2,35</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>2,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,46</t>
+          <t>1,18; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,71</t>
+          <t>1,78; 2,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,86</t>
+          <t>1,36; 1,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,06</t>
+          <t>1,52; 1,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,15</t>
+          <t>1,49; 2,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,13</t>
+          <t>1,7; 2,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,96</t>
+          <t>1,82; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 13,31</t>
+          <t>2,1; 3,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,78</t>
+          <t>1,41; 1,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,26</t>
+          <t>1,79; 2,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,31</t>
+          <t>1,67; 2,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,34</t>
+          <t>1,9; 2,58</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,0</t>
+          <t>1,29; 1,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,84</t>
+          <t>1,4; 1,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,78</t>
+          <t>1,41; 1,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,16</t>
+          <t>1,56; 2,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,02</t>
+          <t>1,56; 2,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,96</t>
+          <t>1,49; 2,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,19</t>
+          <t>1,7; 2,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,33</t>
+          <t>1,63; 2,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,86</t>
+          <t>1,49; 1,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,82</t>
+          <t>1,49; 1,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,98</t>
+          <t>1,63; 1,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,1</t>
+          <t>1,67; 2,15</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,49</t>
+          <t>1,28; 1,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,96</t>
+          <t>1,58; 1,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,8</t>
+          <t>1,5; 1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,12</t>
+          <t>1,63; 2,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,87</t>
+          <t>1,64; 1,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,05</t>
+          <t>1,77; 2,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,09</t>
+          <t>1,75; 2,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,53</t>
+          <t>1,84; 2,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,7</t>
+          <t>1,51; 1,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 1,94</t>
+          <t>1,73; 1,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 1,9</t>
+          <t>1,67; 1,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,26</t>
+          <t>1,77; 2,09</t>
         </is>
       </c>
     </row>
